--- a/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
+++ b/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
@@ -1946,6 +1946,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -7850,6 +7851,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -14230,7 +14232,7 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>G: pergunta ao Gerente (fita estreita no polegar do Gerente); V: ao Caixa Veterano (polegar do Caixa Veterano).</t>
+          <t>G: pergunta ao Gerente (fita estreita no indicador do Gerente); V: ao Caixa Veterano (indicador do Caixa Veterano).</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -19206,7 +19208,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Como uma gaveta pesada. Uma vez logo que o rádio chamou. Outra quase um minuto e meio depois.</t>
+          <t>Como uma gaveta pesada. Uma vez logo que o rádio chamou. Outra quase dois minutos depois, logo depois de a imagem voltar.</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -21251,7 +21253,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>O primeiro raspado veio logo depois da ordem. O segundo, pouco antes de a imagem voltar.</t>
+          <t>O primeiro raspado veio logo depois da ordem. O segundo, logo depois de a imagem voltar.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -26599,7 +26601,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>A fita vendida às seis e trinta e um tem 1,2 centímetro. A do kit de primeiros socorros da Gerência, 2,5, a mesma que o Caixa Novato usa no indicador. E há uma tira estreita no polegar do Subgerente.</t>
+          <t>A fita vendida às seis e trinta e um tem 1,2 centímetro. A do kit de primeiros socorros da Gerência, 2,5, a mesma que o Caixa Novato usa no indicador. E há uma tira estreita no indicador do Subgerente.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -26619,7 +26621,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Variante G: ... no polegar do Gerente (tabela A3; a Variante G do Cap. 8 diz "indicador"). | Variante V: ... na base do polegar do Caixa Veterano.</t>
+          <t>Variante G: ... no indicador do Gerente (tabela A3; a Variante G do Cap. 8 diz "indicador"). | Variante V: ... no indicador do Caixa Veterano.</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -27356,7 +27358,7 @@
       <c r="S37" s="12" t="inlineStr"/>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>Fala do impostor (marca A9 no nome). Antes, gesto: ajeita a fita no dedo (A3; em G "indicador"/polegar, em V base do polegar).</t>
+          <t>Fala do impostor (marca A9 no nome). Antes, gesto: ajeita a fita no dedo (A3; em G "indicador"/indicador, em V base do indicador).</t>
         </is>
       </c>
     </row>
@@ -29012,7 +29014,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>O que o registro desmente: o sensor da porta lateral, aberta às seis e trinta e seis, quando nenhum crachá tinha passado, e o crachá dele, às sete e dezesseis, que pretendia ser a chegada; os dígitos do cartão dele no rádio; o saque em nome dele na 0392; a fita da farmácia no polegar e a luva rasgada no cesto.</t>
+          <t>O que o registro desmente: o sensor da porta lateral, aberta às seis e trinta e seis, quando nenhum crachá tinha passado, e o crachá dele, às sete e dezesseis, que pretendia ser a chegada; os dígitos do cartão dele no rádio; o saque em nome dele na 0392; a fita da farmácia no indicador e a luva rasgada no cesto.</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -29032,7 +29034,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Variante G: "dele" = Gerente; saque do resgate da previdência; fita no indicador (Variante G) ou polegar (tabela A3); o horário do crachá não tem valor definido para a G. | Variante V: "dele" = Caixa Veterano; saque das economias da aposentadoria; fita na base do polegar; horário do crachá não definido para a V.</t>
+          <t>Variante G: "dele" = Gerente; saque do resgate da previdência; fita no indicador (Variante G) ou indicador (tabela A3); o horário do crachá não tem valor definido para a G. | Variante V: "dele" = Caixa Veterano; saque das economias da aposentadoria; fita no indicador; horário do crachá não definido para a V.</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
@@ -30385,7 +30387,7 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>fita no polegar (A3), farinha na barra (A6), cartão do rádio (A7)</t>
+          <t>fita no indicador (A3), farinha na barra (A6), cartão do rádio (A7)</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
@@ -30440,7 +30442,7 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>fita (A3: tabela diz polegar, Variante G diz indicador), farinha (A6), cartão (A7)</t>
+          <t>fita (A3: tabela diz indicador, Variante G diz indicador), farinha (A6), cartão (A7)</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -30495,7 +30497,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>fita na base do polegar (A3), farinha (A6), cartão (A7)</t>
+          <t>fita no indicador (A3), farinha (A6), cartão (A7)</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -30509,6 +30511,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
@@ -30621,7 +30624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30718,7 +30721,11 @@
           <t>Unificar: corte e fita no mesmo dedo nas três partidas (ou rasgo no polegar, ou fita no indicador). Lembrar que o Caixa Novato usa fita larga no indicador — o contraste largura 1,2 × 2,5 cm continua a pista.</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10: fita estreita no INDICADOR do impostor nas três partidas (mesmo dedo do rasgo da luva).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -30738,7 +30745,7 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Pela rota, o impostor volta à Gerência às 7h59:54 (+109 s), depois de a câmera voltar (7h59:39). O Novato diz "quase um minuto e meio depois" (Cap. 4) e "pouco antes de a imagem voltar" (Cap. 5).</t>
+          <t>Pela rota, o impostor volta à Gerência às 7h59:54 (+109 s), depois de a câmera voltar (7h59:39). O Novato diz "quase dois minutos depois, logo depois de a imagem voltar" (Cap. 4) e "logo depois de a imagem voltar" (Cap. 5).</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -30746,7 +30753,11 @@
           <t>Mudar a fala para "quase dois minutos depois" / "logo depois de a imagem voltar", ou o raspado vir do fundo do Rack ao reentrar (7h59:39). A grade da janela precisa fechar antes da narração.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr"/>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10: "quase dois minutos depois, logo depois de a imagem voltar" (Caps. 4 e 5).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -30774,7 +30785,11 @@
           <t>Corrigir a tabela: "Completa" só para o Transportador; oculto e vigia "Sempre" (do sistema, nunca humanos). A matriz já segue assim.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10: oculto e vigia sempre presentes, do sistema.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -30802,7 +30817,11 @@
           <t>A Operadora lê o histórico em toda casa; a Estagiária fica como reforço (ela já está na Central).</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (Cap. 2): sem a Estagiária, a Operadora lê.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -30858,7 +30877,11 @@
           <t>Passar a observação à Auditora ou à Cliente do Cofre (que repara em detalhes) nas casas sem a Farmacêutica.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (Cap. 2): sem a Farmacêutica, a Auditora vê.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -30942,7 +30965,11 @@
           <t>Nas casas sem Subgerente: a sugestão do clone passa ao Caixa Veterano; a resposta dupla vira silêncio do Gerente + versão da Operadora.</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (Cap. 2): clone com o Caixa Veterano; só o Gerente responde "Manutenção".</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -30998,7 +31025,11 @@
           <t>O sensor (6h36) e a caixa de 1998 continuam fechando o ponto; a falsa pista do guarda-chuva vira exclusiva das casas de 10+.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (Cap. 4): sem o Padeiro, sai a cena do guarda-chuva.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -31167,6 +31198,70 @@
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Decisão</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gerente humano</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Elenco; Caps. 4, 6, 7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>O Gerente faz o encobrimento das 8h31 em toda partida.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10: o Gerente é sempre do sistema (como o ajudante consciente).</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Decisão</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pegadas sem a Limpeza</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cap. 4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sem o Funcionário da Limpeza, ninguém descreve as pegadas.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A Auditora diz a frase.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F19"/>
@@ -31272,17 +31367,17 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>No polegar do Subgerente</t>
+          <t>No indicador do Subgerente</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>No polegar do Gerente</t>
+          <t>No indicador do Gerente</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>No polegar do Caixa Veterano</t>
+          <t>No indicador do Caixa Veterano</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr"/>
@@ -36603,6 +36698,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>

--- a/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
+++ b/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
@@ -1946,7 +1946,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -7851,7 +7850,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -30423,11 +30421,11 @@
         </is>
       </c>
       <c r="E3" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>casa 6: 5; casa 8: 7; casa 10: 9; casa 12: 11; casa 13: 12</t>
+          <t>casa 8: 7; casa 10: 9; casa 12: 11; casa 13: 12</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -30478,11 +30476,11 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>casa 6: 5; casa 8: 7; casa 10: 9; casa 12: 11; casa 13: 12</t>
+          <t>casa 8: 7; casa 10: 9; casa 12: 11; casa 13: 12</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -30693,7 +30691,11 @@
           <t>Opção 1: casa mínima de G e V passa a 8 (as três partidas ficam com casa 8). Opção 2: em G e V o cossignatário é o Caixa Veterano/Gerente (núcleo) — exige revisar A2. Opção 3: a pergunta final do ajudante aceita o Segurança Interno (apoio, sempre presente).</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10 (opção 1): G e V passam a casa mínima 8, como a S.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -33406,7 +33408,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>G, V</t>
+          <t>nenhuma (todas pedem casa 8)</t>
         </is>
       </c>
       <c r="G2" s="8" t="n">
@@ -36698,7 +36700,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>

--- a/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
+++ b/Claude outputs/Matriz_Carro-Forte_O_Impostor.xlsx
@@ -37,6 +37,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap 8" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variantes Cap 8" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mudanças no docx" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Partidas'!$A$1:$K$4</definedName>
@@ -182,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,6 +215,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -678,41 +680,53 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Contradições e buracos encontrados ao montar a matriz, com proposta. Nada foi alterado na história: cada item espera decisão (regra 10, nada se apaga sem substituição formal).</t>
+          <t>Contradições e buracos encontrados ao montar a matriz, com proposta e a decisão do Mario. Verde = decidido ou aplicado no jogo.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Cores</t>
+          <t>Mudanças no docx</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Amarelo = linha com ponto de ajuste (muda por partida). Laranja = falta fonte / pendência. Verde = coberto.</t>
+          <t>Lista do que mudar no docx da revisão 2 para a revisão 3: texto atual, texto novo e motivo. O docx não foi alterado.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ids</t>
+          <t>Cores</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Personagens pela função, minúsculas, sem acento (gerente, caixa_veterano…). Lugares com hífen (sala-gerencia, arquivo-morto…). Falas: cN-NNN.</t>
+          <t>Amarelo = linha com ponto de ajuste (muda por partida). Laranja = falta fonte / pendência. Verde = coberto.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Ids</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Personagens pela função, minúsculas, sem acento (gerente, caixa_veterano…). Lugares com hífen (sala-gerencia, arquivo-morto…). Falas: cN-NNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Rascunho</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>As perguntas por capítulo são proposta minha a partir das fichas dos capítulos; precisam da sua aprovação.</t>
         </is>
@@ -7629,7 +7643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7850,6 +7864,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -7857,7 +7872,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTA(Pendências!A2:A19)</f>
+        <f>COUNTA(Pendências!A2:A60)-COUNTA(Pendências!F2:F60)</f>
         <v/>
       </c>
     </row>
@@ -7880,6 +7895,17 @@
       </c>
       <c r="B15">
         <f>COUNTIF('Provas e cobertura'!F2:F24,"FALTA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mudanças no docx (para a revisão 3)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTA('Mudanças no docx'!A2:A60)</f>
         <v/>
       </c>
     </row>
@@ -28468,7 +28494,7 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Variante G: igual à referência. | Variante V: diz o próprio nome em voz baixa antes de a Auditora terminar.</t>
+          <t>Variante G: igual à referência. | Variante V (jogo, 05/10): na acusação não diz nome; diz "Fui eu", em voz baixa, durante a reconstrução da Auditora (c8-023).</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
@@ -28614,7 +28640,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>não (sem ele, o Motorista repete a frase pelo rádio)</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
@@ -28637,7 +28663,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>~10h53</t>
+          <t>10h54</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -29170,7 +29196,11 @@
       </c>
       <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Variante G: a última frase vira "E o cabo queimado das oito e trinta e um não era outra coisa: era o mesmo plano, agora escondendo a si mesmo."</t>
+        </is>
+      </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
           <t>toda casa</t>
@@ -29660,7 +29690,11 @@
       </c>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Variante G: "Alguém falou em fraude." (o Gerente é o impostor)</t>
+        </is>
+      </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
           <t>toda casa</t>
@@ -29753,7 +29787,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>11h05</t>
+          <t>10h57</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -29778,7 +29812,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Para a ata: o impostor responderá pela custódia violada, pelo uso indevido de credencial, pela sabotagem da câmera, pela ordem falsa e pela exposição dos colegas. O Gerente responderá pela destruição de evidência e pela saída daquela noite. O Técnico, pela conta e pelas peças sem nota. A Estagiária, a Farmacêutica, a Operadora, o Funcionário da Limpeza e os seguranças terão as falhas registradas com o contexto ao lado. O Caixa Novato não responderá por ter tido medo.</t>
+          <t>Para a ata: [a função de quem trocou o malote] responderá pela custódia violada, pelo uso indevido de credencial, pela sabotagem da câmera, pela ordem falsa e pela exposição dos colegas…</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -29788,7 +29822,11 @@
       </c>
       <c r="I35" s="9" t="inlineStr"/>
       <c r="J35" s="9" t="inlineStr"/>
-      <c r="K35" s="9" t="inlineStr"/>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Sem a palavra "impostor" (05/10). Variante G: o Gerente responde também pela destruição de evidência e pela saída daquela noite. Todas: o ajudante, pela assinatura sem contagem.</t>
+        </is>
+      </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
           <t>toda casa</t>
@@ -29930,7 +29968,7 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Variante G: igual. | Variante V: o Veterano já saiu; o Novato aprende a ouvir o Cofre com o Subgerente, e a fala é dita pelo Novato como lembrança do Veterano.</t>
+          <t>Variante G: igual. | Variante V (jogo, 05/10): o Subgerente ensina; o Caixa Novato diz a frase, repetindo quem lhe ensinara primeiro.</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
@@ -30213,7 +30251,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>O Gerente aponta o Técnico com mais força; a Cliente do Cofre mantém a desconfiança dele.</t>
+          <t>O Gerente aponta o Técnico com mais força; a Cliente do Cofre mantém a desconfiança dele. Jogo (05/10): "Alguém falou em fraude" (no lugar do Gerente); "o cabo queimado das oito e trinta e um não era outra coisa: era o mesmo plano, agora escondendo a si mesmo"; na separação dos atos, o Gerente responde também pela destruição de evidência e pela saída daquela noite.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -30250,12 +30288,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>O Caixa Veterano diz o próprio nome em voz baixa antes de a Auditora terminar.</t>
+          <t>Docx: o Caixa Veterano diz o próprio nome em voz baixa antes de a Auditora terminar. Jogo (05/10): na acusação não diz nome, como na S; diz "Fui eu", em voz baixa, durante a reconstrução, antes de a Auditora terminar.</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>O Caixa Novato aprende a ouvir o Cofre com o Subgerente; a fala "Não é magia. É atenção" fica como lembrança do Veterano, dita pelo Novato. Sai do epílogo o Veterano pendurando a fotografia antes de ir (passa para a saída).</t>
+          <t>O Caixa Novato aprende a ouvir o Cofre com o Subgerente; a fala "Não é magia. É atenção" fica como lembrança do Veterano, dita pelo Novato. Sai do epílogo o Veterano pendurando a fotografia antes de ir (passa para a saída). Jogo (05/10): o Caixa Novato diz "Não é magia. É atenção.", repetindo quem lhe ensinara primeiro.</t>
         </is>
       </c>
     </row>
@@ -30509,7 +30547,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
@@ -30622,7 +30659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30666,368 +30703,384 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Ajudante fora da casa de 6 (G e V)</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Cânone, Pontos de ajuste A2; Cap. 7; pergunta final "quem ajudou"</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Nas partidas G e V o ajudante (cossignatário A2) é o Subgerente, do 1º bloco. Na casa de 6 ele não existe: some a confissão "assinei sem contar" e a pergunta final "quem o ajudou?" fica sem resposta possível.</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Opção 1: casa mínima de G e V passa a 8 (as três partidas ficam com casa 8). Opção 2: em G e V o cossignatário é o Caixa Veterano/Gerente (núcleo) — exige revisar A2. Opção 3: a pergunta final do ajudante aceita o Segurança Interno (apoio, sempre presente).</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>DECIDIDO 05/10 (opção 1): G e V passam a casa mínima 8, como a S.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Fita no dedo × luva rasgada</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>A3 (Caps. 2, 7, 8); luva do Cap. 6</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>A luva tem o rasgo e o sangue no INDICADOR, mas a fita do impostor está no POLEGAR (S e V; a tabela A3 também diz polegar para G, enquanto a Variante G diz indicador).</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Unificar: corte e fita no mesmo dedo nas três partidas (ou rasgo no polegar, ou fita no indicador). Lembrar que o Caixa Novato usa fita larga no indicador — o contraste largura 1,2 × 2,5 cm continua a pista.</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>DECIDIDO 05/10: fita estreita no INDICADOR do impostor nas três partidas (mesmo dedo do rasgo da luva).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Segundo raspado da parede</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Caps. 4 e 5 (Caixa Novato)</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Pela rota, o impostor volta à Gerência às 7h59:54 (+109 s), depois de a câmera voltar (7h59:39). O Novato diz "quase dois minutos depois, logo depois de a imagem voltar" (Cap. 4) e "logo depois de a imagem voltar" (Cap. 5).</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Mudar a fala para "quase dois minutos depois" / "logo depois de a imagem voltar", ou o raspado vir do fundo do Rack ao reentrar (7h59:39). A grade da janela precisa fechar antes da narração.</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>DECIDIDO 05/10: "quase dois minutos depois, logo depois de a imagem voltar" (Caps. 4 e 5).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Oculto e vigia: bloco "Completa" × "sempre presentes"</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Tabela "As quinze funções"</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>A tabela põe o Monitor Remoto e o Operador de Rádio no bloco "Completa", mas o Guia (4.3) e a própria cobertura os tratam como presentes em toda casa (mensagem 8h10, reimpressão, 6h52, 8h29, 9h31, 9h56).</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Corrigir a tabela: "Completa" só para o Transportador; oculto e vigia "Sempre" (do sistema, nunca humanos). A matriz já segue assim.</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>APLICADO 05/10: oculto e vigia sempre presentes, do sistema.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Faixa administrativa lida só pela Estagiária</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Cap. 2</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>O histórico do rádio (pareamento 7h57:55) e a lista de quem tem cartão na faixa só são ditos pela Estagiária (3º bloco). Na casa de 6, a pergunta secundária do Cap. 2 fica sem fonte.</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>A Operadora lê o histórico em toda casa; a Estagiária fica como reforço (ela já está na Central).</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>APLICADO 05/10 (Cap. 2): sem a Estagiária, a Operadora lê.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Quem tem chave da porta lateral, na casa de 6</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Cap. 5</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>A lista da escala é dita pelo Subgerente e o "Eu" pela Limpeza (1º bloco). Na casa de 6 só o Técnico responde.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Na ausência do Subgerente, a lista da escala sai do Gerente ou do Caixa Veterano; a chave da Limpeza vem do registro de chaves (Operadora).</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>RESOLVIDO 05/10 pela casa mínima 8: o Subgerente e a Limpeza estão sempre na casa. A chave da Limpeza também consta no registro de chaves (Operadora).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Plantação da fita estreita no Cap. 2</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Cap. 2 (Farmacêutica)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>A observação das duas fitas (larga no Novato, estreita no impostor) só existe pela Farmacêutica (3º bloco). Nas casas de 6 a 10 a pista do Cap. 7 não tem plantação.</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Passar a observação à Auditora ou à Cliente do Cofre (que repara em detalhes) nas casas sem a Farmacêutica.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>APLICADO 05/10 (Cap. 2): sem a Farmacêutica, a Auditora vê.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Falas fixas do Cap. 8 que contradizem a partida G</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Cap. 8 (narração da Auditora); Cap. 7 ("Não toquei no malote")</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>"O Gerente tinha um cabo queimado… mas era outra coisa" e "O Gerente quis falar de fraude" não servem quando o Gerente é o impostor. "Não toquei no malote" é mentira essencial em G — precisa ser desmontada.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Marcar esses trechos como pontos de ajuste (A9/A11) com variante G.</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 8): na G, "Alguém falou em fraude" e "o cabo queimado das oito e trinta e um não era outra coisa: era o mesmo plano, agora escondendo a si mesmo". Cap. 7, "Não toquei no malote": mantido; na G é mentira do próprio impostor (permitida). Falta aplicar no docx (aba Mudanças no docx).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Palavra "impostor" no texto público</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Cap. 8 (separação dos atos)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>"O impostor responderia pela custódia violada…" usa vocabulário do guia no texto público.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Trocar por "Quem trocou o malote responderia…" ou pela função.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 8): a função entra no lugar ("O Subgerente responderia…"). Falta aplicar no docx.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Respostas que perdem o par quando o Subgerente sai</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Caps. 2 e 4</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>"Possível. Com equipamento." (Técnico) responde a "Talvez tenham clonado algum"; "Duas respostas para uma única conversa" depende do "Pessoal".</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Nas casas sem Subgerente: a sugestão do clone passa ao Caixa Veterano; a resposta dupla vira silêncio do Gerente + versão da Operadora.</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>APLICADO 05/10 (Cap. 2): clone com o Caixa Veterano; só o Gerente responde "Manutenção".</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Perguntas do núcleo a personagens de bloco</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Cap. 1 (Gerente → Limpeza; Auditora → Segurança do Veículo)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Sem a Limpeza ou o Segurança do Veículo, as perguntas ficam sem resposta e a mentira da chave não acontece.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Na casa sem o personagem, a pergunta sai do roteiro (condição de presença na coluna "Condição").</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 1): a Limpeza está sempre na casa (casa mínima 8); sem o Segurança do Veículo, a pergunta da Auditora sai do roteiro.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Figura das 6h28 só pelo Padeiro</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Caps. 4 e 5</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Sem o Padeiro (casas de 6 e 8), some a falsa pista do guarda-chuva da Auditora e a pergunta "a sacola ficou lá dentro. Onde?".</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>O sensor (6h36) e a caixa de 1998 continuam fechando o ponto; a falsa pista do guarda-chuva vira exclusiva das casas de 10+.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>APLICADO 05/10 (Cap. 4): sem o Padeiro, sai a cena do guarda-chuva.</t>
         </is>
@@ -31059,7 +31112,11 @@
           <t>Corrigir os quadros.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>PARA O DOCX: trocar "Estagiária no terminal" por "Operadora no terminal" (aba Mudanças no docx). O jogo já segue a narrativa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -31087,91 +31144,107 @@
           <t>Corrigir a direção interna.</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>PARA O DOCX: "6h36 aberta por chave mecânica; 7h06 aberta pela barra, por dentro"; a cinta é achada pelo Caixa Veterano (aba Mudanças no docx).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Hora do checksum</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Cap. 7 e Quadro final</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Texto: pareamento chega "quase no mesmo minuto" que a regional (10h41); ficha: 10h46. Quadro final dá 11h05 à separação dos atos, que no texto vem antes das 10h58.</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Alinhar as âncoras.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo): âncoras 10h41 (titular) e 10h46 (checksum), com "Cinco minutos depois" no lugar de "quase no mesmo minuto"; no Cap. 8: 10h52 acusação, 10h54 a Auditora retoma, 10h57 separação dos atos, 10h58 contagem final, 11h12 a porta. Falta aplicar no docx.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>"Eu vi às oito e vinte" (Farmacêutica)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Cap. 7</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Não diz o que ela viu. Se for a fita no dedo do impostor, é ponto de ajuste.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Explicitar e marcar A3.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 7): "Eu vi a fita estreita às oito e vinte." Marcar A3 no docx.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>"Não imprimi nada" (Caixa Veterano, Cap. 1)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Cap. 1</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Na partida V ele é o impostor e agendou a impressão às 6h58. Literalmente verdade (ninguém imprimiu às 7h53), mas convém conferir a voz.</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Manter; registrar como mentira por omissão permitida.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>MANTIDO 05/10: mentira por omissão permitida na partida V (ninguém imprimiu às 7h53; a impressão foi agendada às 6h58).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -31202,71 +31275,945 @@
       <c r="F19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Decisão</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Gerente humano</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Elenco; Caps. 4, 6, 7</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>O Gerente faz o encobrimento das 8h31 em toda partida.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>DECIDIDO 05/10: o Gerente é sempre do sistema (como o ajudante consciente).</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>DECIDIDO 05/10</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Decisão</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Pegadas sem a Limpeza</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Cap. 4</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Sem o Funcionário da Limpeza, ninguém descreve as pegadas.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>A Auditora diz a frase.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>APLICADO 05/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Caixa Veterano se denuncia antes das perguntas (V)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Cap. 8, acusação (Variante V)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Na Variante V, o Caixa Veterano diz o próprio nome na rodada da acusação, antes da pergunta final "Quem é o impostor?": entregaria a resposta.</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Na rodada da acusação ele não diz nome (como na S); diz "Fui eu", em voz baixa, durante a reconstrução da Auditora, "antes de a Auditora terminar".</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 8). Falta aplicar no docx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>"Não é magia. É atenção." na partida V</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Cap. 8, epílogo</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Na V o Caixa Veterano já saiu; a fala precisa de outro dono.</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>O Subgerente ensina o Novato a ouvir o Cofre; o Caixa Novato diz a frase, repetindo quem lhe ensinara primeiro.</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Pergunta secundária S2 do Cap. 6</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Aba Perguntas; Cap. 6</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>"Quem assinou sem contagem?" não tinha resposta completa no texto do capítulo.</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Trocar por "O que aconteceu às 19h03?" (a trava).</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, Cap. 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Substituições por ausência (casas de 8 a 12)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Caps. 1 a 8</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Falas que dependem de personagens de bloco somem nas casas menores.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Regras de substituição usadas no jogo: rádio lido pela Operadora (sem a Estagiária); fitas vistas pela Auditora (sem a Farmacêutica); clone sugerido pelo Caixa Veterano (sem o Subgerente); pegadas ditas pela Auditora (sem a Limpeza); sem o Padeiro, sai a cena do guarda-chuva e a Auditora pergunta pela sacola; sem a Limpeza no Cap. 6, a Auditora deduz o saco pela tampa (7h59:24), o balde (8h01) e o saco (8h02); sem o Transportador, o Motorista repete "Ninguém tirou. Alguém pôs."</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo). No docx, vale registrar na nota interna de cada capítulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Decisão</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Pontuação final</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Cap. 8; Guia técnico</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>A pergunta final tem pesos diferentes.</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Impostor ×3, ajudante ×2, mecanismo e intenção ×1; secundária vale metade. Com certeza ±4; sem certeza +2/−1; não sei 0. Apostas por capítulo não pontuam: aparecem no placar.</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>APLICADO 05/10 (jogo, placar).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Capítulo / seção</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Onde</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Texto atual (revisão 2)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Texto novo (proposta para a revisão 3)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Motivo / decisão</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Notas internas · Pontos de ajuste</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Tabela A3</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>A3. O corte coberto por fita microporosa estreita (1,2 cm): No polegar do Subgerente | No polegar do Gerente | No polegar do Caixa Veterano</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>… No indicador do Subgerente | No indicador do Gerente | No indicador do Caixa Veterano</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10: fita no indicador nas três partidas (mesmo dedo do rasgo da luva).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Notas internas · Quem nunca é o impostor</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Tabela "Nunca é o impostor"</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>(sem linha para o Gerente humano)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Acrescentar: "O Gerente (vestido por humano) · Nunca recebe humano: faz o encobrimento das 8h31 em toda partida, ato consciente que um jogador não pode ser obrigado a fazer."</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10: o Gerente é sempre do sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Notas internas · As quinze funções</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Tabela das funções e blocos</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Completa · O oculto · O Monitor Remoto / Completa · O vigia de fora · O Operador de Rádio</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Sempre (do sistema) · O oculto · O Monitor Remoto / Sempre (do sistema) · O vigia de fora · O Operador de Rádio. "Completa" fica só para o Transportador.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Aplicado 05/10: oculto e vigia presentes em toda casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Notas internas · Casa mínima por partida</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Parágrafo "Casa mínima por partida"</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Partida G (Gerente) e partida V (Caixa Veterano): casa de 6. Partida S (Subgerente): casa de 8, a primeira que o inclui; […] Nas casas em que o Subgerente não está, as ações fixas dele […] saem.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>As três partidas têm casa mínima de 8: o Subgerente é o impostor na S e o ajudante (cossignatário A2) na G e na V, e por isso precisa estar na casa. Na casa de 8 entram também o Funcionário da Limpeza. (Apagar a frase sobre as casas sem o Subgerente.)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (opção 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Notas internas · A conta do caso</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Parágrafo "A conta do caso"</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Mesas: de 1 a 5 humanos na casa de 6 (G e V), e assim por diante pelos blocos; o impostor nunca recebe humano.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Mesas: a partir da casa de 8, com 1 a 6 humanos nas partidas S e V e 1 a 7 na G, e assim por diante pelos blocos; o impostor e o Gerente nunca recebem humano.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Consequência da casa mínima 8 e do Gerente sempre do sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 2</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>A Farmacêutica observa mãos</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>uma tira estreita e limpa no polegar do Subgerente^A3^.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>uma tira estreita e limpa no indicador do Subgerente^A3^.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (A3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 4</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>O Caixa Novato no banheiro</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>— Como uma gaveta pesada. Uma vez logo que o rádio chamou. Outra quase um minuto e meio depois.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>— Como uma gaveta pesada. Uma vez logo que o rádio chamou. Outra quase dois minutos depois, logo depois de a imagem voltar.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10: pela rota, o impostor volta à Gerência às 7h59:54, depois de a câmera voltar (7h59:39).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 4</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Quadro interno, 8h51</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Estagiária no terminal; Técnico corre ao Rack</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Operadora no terminal; Técnico corre ao Rack</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Na narrativa é a Operadora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 5</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>O Caixa Novato conta nos dedos</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>O primeiro raspado viera logo depois da ordem. O segundo, pouco antes de a imagem voltar.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>O primeiro raspado viera logo depois da ordem. O segundo, logo depois de a imagem voltar.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (mesma correção do Cap. 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 5</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Quadro interno, 6h36 e 7h06</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Duas aberturas por chave mecânica</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>6h36: aberta por chave mecânica; 7h06: aberta pela barra, por dentro</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>O registro do sensor (Cap. 5) diz que às 7h06 a porta foi aberta pela barra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 5</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Ficha, "Subtrama que avança"</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>O Técnico admite a atualização; a Limpeza encontra a cinta na caixa</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>O Técnico admite a atualização; o Caixa Veterano encontra a cinta na caixa de 1998 (a Limpeza conta que a empurrara de volta às 7h46)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>No texto, quem puxa a caixa e lê a cinta é o Caixa Veterano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 6</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Quadro interno, 10h04</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Estagiária no terminal; todos no Saguão</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Operadora no terminal; todos no Saguão</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Na narrativa é a Operadora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 7</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>A Auditora compara as fitas</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Ela olhou para a tira estreita no polegar do Subgerente^A3^.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Ela olhou para a tira estreita no indicador do Subgerente^A3^.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (A3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 7</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>A Farmacêutica</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>— Eu vi às oito e vinte. Não disse porque teria de contar o resto.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>— Eu vi a fita estreita às oito e vinte.^A3^ Não disse porque teria de contar o resto.</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Explicitar o que ela viu; é ponto de ajuste (a mão muda por partida).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 7</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>O retorno do fornecedor do rádio</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>A Operadora recebeu, quase no mesmo minuto, o retorno do fornecedor do rádio […]</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Cinco minutos depois, a Operadora recebeu o retorno do fornecedor do rádio […]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Alinha o texto à âncora do checksum (10h46) e ao titular (10h41).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>"O que o registro desmente"</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>[…] a fita da farmácia no polegar^A3^ e a luva rasgada no cesto.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>[…] a farinha da padaria na barra da calça^A6^; a fita da farmácia no indicador^A3^ e a luva rasgada no cesto.</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (A3); a farinha (A6) entra na lista porque já foi provada no Cap. 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Separação dos atos</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Ela separou os atos em voz alta, para a ata. O impostor responderia pela custódia violada […]</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Ela separou os atos em voz alta, para a ata. O Subgerente^A9^ responderia pela custódia violada […]</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>A palavra "impostor" é do guia, não do texto público. Na G e na V entra a função da partida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Quadro final, 11h05</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>11h05 · Auditora com a ata; todos no Saguão · Os atos são separados</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>10h57 · Auditora com a ata; todos no Saguão · Os atos são separados (antes da contagem final das 10h58)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>No texto, a separação dos atos vem antes da contagem final. Âncoras usadas no jogo: 10h52 acusação, 10h54 a Auditora retoma, 10h57 atos, 10h58 contagem, 11h12 a porta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8 · Variante G</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Parágrafo da Variante G (acrescentar)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>(não trata da narração da Auditora)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Acrescentar: "Na narração da Auditora, 'O Gerente tinha um cabo queimado, que era seu de fato, mas era outra coisa' vira 'E o cabo queimado das oito e trinta e um não era outra coisa: era o mesmo plano, agora escondendo a si mesmo'; 'O Gerente quis falar de fraude' vira 'Alguém falou em fraude'. Na separação dos atos, o Gerente responde também pela destruição de evidência e pela saída daquela noite."</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Pendência "Falas fixas do Cap. 8 que contradizem a partida G".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8 · Variante V</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Parágrafo da Variante V</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>A3, A6, A7, A8: a fita na base do polegar, a farinha na barra […]</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>A3, A6, A7, A8: a fita no indicador, a farinha na barra […]</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Decisão 05/10 (A3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Cap. 8 · Variante V</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Parágrafo da Variante V</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Na acusação, o Caixa Veterano diz o próprio nome em voz baixa antes da Auditora terminar.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Na acusação, o Caixa Veterano não diz nome, como na referência. Durante a reconstrução, antes de a Auditora terminar, ele diz em voz baixa: "Fui eu."</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Na acusação, ele se entregaria antes da pergunta final do jogador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Todos os capítulos</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Nota interna de cada capítulo</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>(sem regras de ausência)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Registrar as substituições por ausência usadas no jogo (aba Pendências, linha "Substituições por ausência").</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Para que o docx e o jogo digam a mesma coisa nas casas de 8 a 12.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31382,7 +32329,11 @@
           <t>No indicador do Caixa Veterano</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>DECIDIDO 05/10: indicador nas três partidas (o docx ainda diz polegar).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -31600,7 +32551,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Proposta: marcar como A5 também a fala do Gerente e a do Caixa Veterano no Cap. 4.</t>
+          <t>APLICADO 05/10 (jogo, Cap. 4: declarações; Cap. 7: gavetas). Marcar A5 no docx.</t>
         </is>
       </c>
     </row>
@@ -31627,7 +32578,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Valores já existem no Cap. 2 (registro dos crachás); falta só marcar o ponto.</t>
+          <t>APLICADO 05/10 (jogo, Cap. 8). Marcar A5 no docx.</t>
         </is>
       </c>
     </row>
